--- a/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,17 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>PE Clause did not load as expected (url_ok=True, heading_ok=False, placeholder_ok=False).</t>
+          <t>PE Clause loaded correctly at https://regplus.kaz.com.bd/wta/PEClauses.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] PE Clause loads with URL/heading/placeholder all present</t>
+          <t>[PASS] PE Clause loads with URL/heading/placeholder all present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -620,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the PE clause table with the expected headers and 45 rows.</t>
+          <t>Selecting Australia rendered the PE clause table with the expected headers and 43 rows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,7 +620,7 @@
           <t>[PASS] PE clause table shows the expected columns and at least one row</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -687,7 +679,7 @@
           <t>[PASS] The 'Austria' row contains 'Art. 5(1)'</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -746,7 +738,7 @@
           <t>[PASS] 'Belgium' is visible under the Europe region tab</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -805,7 +797,7 @@
           <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -814,35 +806,155 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>PEClauses_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Treaties PEClauses</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking an article-reference link opens the treaty article modal</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on PE Clause.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria, column: Fixed Base</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open PE Clause
+2. Select Australia
+3. Click the 'Art. 5(1)' link in the Austria row
+4. Verify the article modal title</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The article modal opens with the correct treaty title</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PEClauses_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Treaties PEClauses</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's PDF export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open PE Clause, select Australia
+2. Open the Austria article modal
+3. Click 'PDF' under Export
+4. Verify a real, non-empty PDF download completed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PDF export downloaded 'AU_AT_Art. 5(1)_Treaty_Article.pdf' (17532 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>PEClauses_08</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Treaties PEClauses</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>The table-level 'Export as Excel' button downloads the whole table</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on PE Clause.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
 2. Select Australia
@@ -850,22 +962,22 @@
 4. Verify a real, non-empty .xlsx download completed</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_PEClause.xlsx' (4632 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_PEClause.xlsx' (4578 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_01</t>
+          <t>PEClauses_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PE Clause page loads with the jurisdiction panel</t>
+          <t>The Austria row shows the expected Fixed Base article reference</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load at /wta/PEClauses with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
+          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on PE Clause.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
-2. Verify URL, heading and placeholder text</t>
+2. Select Australia
+3. Verify the 'Austria' row contains 'Art. 5(1)'</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load at /wta/PEClauses with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
+          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>PE Clause loaded correctly at https://regplus.kaz.com.bd/wta/PEClauses.</t>
+          <t>The 'Austria' row correctly shows 'Art. 5(1)' as its Fixed Base article reference.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] PE Clause loads with URL/heading/placeholder all present</t>
+          <t>[PASS] The 'Austria' row contains 'Art. 5(1)'</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_02</t>
+          <t>PEClauses_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +581,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders the PE clause table</t>
+          <t>Switching the 'Europe' region tab shows a European jurisdiction</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Fixed Base', 'Construction Assembly', 'Dependent Agent', 'Services', 'Exempt PE'] and multiple rows.</t>
+          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -595,29 +596,29 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>Region: Europe, expected country: Belgium</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
-2. Select Australia
-3. Verify the table headers and row count</t>
+2. Click the 'Europe' region tab
+3. Verify 'Belgium' is visible in the jurisdiction list</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Fixed Base', 'Construction Assembly', 'Dependent Agent', 'Services', 'Exempt PE'] and multiple rows.</t>
+          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the PE clause table with the expected headers and 43 rows.</t>
+          <t>Switching to the 'Europe' region tab made 'Belgium' visible in the jurisdiction list.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] PE clause table shows the expected columns and at least one row</t>
+          <t>[PASS] 'Belgium' is visible under the Europe region tab</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -629,7 +630,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_03</t>
+          <t>PEClauses_05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -639,44 +640,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The Austria row shows the expected Fixed Base article reference</t>
+          <t>Searching for a non-existent country shows the 'No countries found' message</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on PE Clause.</t>
+          <t>User is logged in and on PE Clause.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia, partner: Austria</t>
+          <t>Search text: zzzznotarealcountry</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
-2. Select Australia
-3. Verify the 'Austria' row contains 'Art. 5(1)'</t>
+2. Type 'zzzznotarealcountry' into the search box
+3. Verify the 'No countries found' message is shown</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The 'Austria' row correctly shows 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The 'Austria' row contains 'Art. 5(1)'</t>
+          <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -688,7 +689,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_04</t>
+          <t>PEClauses_06</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -698,143 +699,25 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Switching the 'Europe' region tab shows a European jurisdiction</t>
+          <t>Clicking an article-reference link opens the treaty article modal</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
+          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on PE Clause.</t>
+          <t>User is logged in, Australia selected on PE Clause.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Region: Europe, expected country: Belgium</t>
+          <t>Country: Australia, partner: Austria, column: Fixed Base</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open PE Clause
-2. Click the 'Europe' region tab
-3. Verify 'Belgium' is visible in the jurisdiction list</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Switching to the 'Europe' region tab made 'Belgium' visible in the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Belgium' is visible under the Europe region tab</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country shows the 'No countries found' message</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on PE Clause.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Search text: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open PE Clause
-2. Type 'zzzznotarealcountry' into the search box
-3. Verify the 'No countries found' message is shown</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking an article-reference link opens the treaty article modal</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on PE Clause.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria, column: Fixed Base</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
 2. Select Australia
@@ -842,59 +725,59 @@
 4. Verify the article modal title</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] The article modal opens with the correct treaty title</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>PEClauses_07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Treaties PEClauses</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>The article modal's PDF export downloads a real, non-empty file</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open PE Clause, select Australia
 2. Open the Austria article modal
@@ -902,59 +785,59 @@
 4. Verify a real, non-empty PDF download completed</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>PDF export downloaded 'AU_AT_Art. 5(1)_Treaty_Article.pdf' (17532 bytes) successfully.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>PEClauses_08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Treaties PEClauses</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>The table-level 'Export as Excel' button downloads the whole table</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on PE Clause.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
 2. Select Australia
@@ -962,22 +845,22 @@
 4. Verify a real, non-empty .xlsx download completed</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_PEClause.xlsx' (4578 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_PEClause.xlsx' (4632 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties PEClauses/Treaties PEClauses_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_03</t>
+          <t>PEClauses_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,44 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Austria row shows the expected Fixed Base article reference</t>
+          <t>PE Clause page loads with the jurisdiction panel</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>The page must load at /wta/PEClauses with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on PE Clause.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia, partner: Austria</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
-2. Select Australia
-3. Verify the 'Austria' row contains 'Art. 5(1)'</t>
+2. Verify URL, heading and placeholder text</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the row for 'Austria' must show 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>The page must load at /wta/PEClauses with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The 'Austria' row correctly shows 'Art. 5(1)' as its Fixed Base article reference.</t>
+          <t>PE Clause loaded correctly at https://regplusrc.reganalytics.com/wta/PEClauses.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The 'Austria' row contains 'Art. 5(1)'</t>
+          <t>[PASS] PE Clause loads with URL/heading/placeholder all present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PEClauses_04</t>
+          <t>PEClauses_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,12 +580,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching the 'Europe' region tab shows a European jurisdiction</t>
+          <t>Selecting a jurisdiction renders the PE clause table</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
+          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Fixed Base', 'Construction Assembly', 'Dependent Agent', 'Services', 'Exempt PE'] and multiple rows.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,271 +595,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Region: Europe, expected country: Belgium</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open PE Clause
-2. Click the 'Europe' region tab
-3. Verify 'Belgium' is visible in the jurisdiction list</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Europe' region tab must make a known European country (e.g. 'Belgium') visible in the left jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Switching to the 'Europe' region tab made 'Belgium' visible in the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Belgium' is visible under the Europe region tab</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_05</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country shows the 'No countries found' message</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on PE Clause.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Search text: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open PE Clause
-2. Type 'zzzznotarealcountry' into the search box
-3. Verify the 'No countries found' message is shown</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message and hide the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_06</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking an article-reference link opens the treaty article modal</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on PE Clause.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria, column: Fixed Base</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open PE Clause
 2. Select Australia
-3. Click the 'Art. 5(1)' link in the Austria row
-4. Verify the article modal title</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the 'Art. 5(1)' link in the Austria row's 'Fixed Base' column must open a modal titled 'Treaty between Australia and Austria' - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The article modal opens with the correct treaty title</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_07</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The article modal's PDF export downloads a real, non-empty file</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected, Austria's article modal open.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open PE Clause, select Australia
-2. Open the Austria article modal
-3. Click 'PDF' under Export
-4. Verify a real, non-empty PDF download completed</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>PDF export downloaded 'AU_AT_Art. 5(1)_Treaty_Article.pdf' (17532 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>PEClauses_08</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties PEClauses</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The table-level 'Export as Excel' button downloads the whole table</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on PE Clause.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open PE Clause
-2. Select Australia
-3. Click the 'Export as Excel' icon button
-4. Verify a real, non-empty .xlsx download completed</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_PEClause.xlsx' (4632 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+3. Verify the table headers and row count</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Fixed Base', 'Construction Assembly', 'Dependent Agent', 'Services', 'Exempt PE'] and multiple rows.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Australia rendered the PE clause table with the expected headers and 45 rows.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] PE clause table shows the expected columns and at least one row</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
